--- a/data/trans_orig/Q04C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda</t>
+          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,1; 32,98</t>
+          <t>29,33; 33,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,18; 35,98</t>
+          <t>33,32; 35,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,14; 34,4</t>
+          <t>32,07; 34,22</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 19,32</t>
+          <t>17,82; 19,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,7; 22,09</t>
+          <t>18,75; 21,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,58; 20,92</t>
+          <t>18,56; 20,75</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,99; 18,84</t>
+          <t>15,86; 18,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 18,72</t>
+          <t>16,47; 18,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 18,3</t>
+          <t>16,56; 18,28</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,57; 20,93</t>
+          <t>19,59; 20,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,74; 23,22</t>
+          <t>21,72; 23,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,94; 22,15</t>
+          <t>20,91; 22,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Estudios-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>31,12</t>
+          <t>29,54</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34,66</t>
+          <t>34,0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33,21</t>
+          <t>32,14</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,33; 33,01</t>
+          <t>27,67; 31,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,32; 35,92</t>
+          <t>32,71; 35,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,07; 34,22</t>
+          <t>31,05; 33,25</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,55</t>
+          <t>17,91</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,93</t>
+          <t>18,42</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,27</t>
+          <t>18,16</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 19,43</t>
+          <t>17,07; 18,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 21,97</t>
+          <t>17,82; 19,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,56; 20,75</t>
+          <t>17,64; 18,68</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,27</t>
+          <t>16,59</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17,54</t>
+          <t>16,81</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,41</t>
+          <t>16,7</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 18,78</t>
+          <t>15,16; 17,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 18,65</t>
+          <t>15,63; 17,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 18,28</t>
+          <t>15,82; 17,52</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>19,57</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,42</t>
+          <t>21,54</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,44</t>
+          <t>20,57</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,59; 20,98</t>
+          <t>18,88; 20,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,72; 23,24</t>
+          <t>20,92; 22,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 22,06</t>
+          <t>20,14; 21,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Estudios-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
+          <t>Tiempo medio en años que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
